--- a/서버정보/20260703_리소스배포_개발.xlsx
+++ b/서버정보/20260703_리소스배포_개발.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FB61B1-141E-49E3-A424-AFE99040A228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F60E9C-EF17-404E-AEC1-9C5A37979C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1957,10 +1957,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10.156.152.10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>D2S_V5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1977,6 +1973,10 @@
   </si>
   <si>
     <t>/subscriptions/b73b1d70-b43f-41b5-bb3f-34b9236d2ed9/resourceGroups/hazr-l-mgmt-rg/providers/Microsoft.Compute/galleries/hazrlmgmtgal/images/RHEL_9.6_nginx_Base_Image/versions/0.0.9</t>
+  </si>
+  <si>
+    <t>10.156.162.10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4221,7 +4221,7 @@
         <v>191</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O2" s="1" t="str">
         <f t="shared" ref="O2:O30" si="0">SUBSTITUTE(F2,"hazr-","")&amp;"-osdisk"</f>
@@ -4310,7 +4310,7 @@
         <v>191</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O3" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4399,7 +4399,7 @@
         <v>191</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O4" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4488,7 +4488,7 @@
         <v>191</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O5" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4577,7 +4577,7 @@
         <v>191</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4666,7 +4666,7 @@
         <v>191</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O7" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4755,7 +4755,7 @@
         <v>191</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O8" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4844,7 +4844,7 @@
         <v>191</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O9" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4933,7 +4933,7 @@
         <v>191</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O10" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5022,7 +5022,7 @@
         <v>191</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O11" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5111,7 +5111,7 @@
         <v>191</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O12" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5200,7 +5200,7 @@
         <v>191</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O13" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5289,7 +5289,7 @@
         <v>191</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O14" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5378,7 +5378,7 @@
         <v>191</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O15" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5467,7 +5467,7 @@
         <v>191</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O16" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5556,7 +5556,7 @@
         <v>191</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O17" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5645,7 +5645,7 @@
         <v>191</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O18" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5734,7 +5734,7 @@
         <v>191</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O19" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5823,7 +5823,7 @@
         <v>191</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O20" s="1" t="str">
         <f t="shared" si="0"/>
@@ -5912,7 +5912,7 @@
         <v>191</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O21" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6001,7 +6001,7 @@
         <v>191</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O22" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6090,7 +6090,7 @@
         <v>191</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O23" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6179,7 +6179,7 @@
         <v>191</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O24" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6268,7 +6268,7 @@
         <v>191</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O25" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6357,7 +6357,7 @@
         <v>191</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O26" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6446,7 +6446,7 @@
         <v>191</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O27" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6535,7 +6535,7 @@
         <v>191</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O28" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6624,7 +6624,7 @@
         <v>191</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O29" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6713,7 +6713,7 @@
         <v>191</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O30" s="1" t="str">
         <f t="shared" si="0"/>
@@ -6802,7 +6802,7 @@
         <v>191</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O31" s="1" t="str">
         <f t="shared" ref="O31:O45" si="2">SUBSTITUTE(F31,"hazr-","")&amp;"-osdisk"</f>
@@ -6891,7 +6891,7 @@
         <v>191</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O32" s="1" t="str">
         <f t="shared" si="2"/>
@@ -6980,7 +6980,7 @@
         <v>191</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O33" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7069,7 +7069,7 @@
         <v>191</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O34" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7158,7 +7158,7 @@
         <v>191</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O35" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7247,7 +7247,7 @@
         <v>191</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O36" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7336,7 +7336,7 @@
         <v>191</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O37" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7425,7 +7425,7 @@
         <v>191</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O38" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7514,7 +7514,7 @@
         <v>191</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O39" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7603,7 +7603,7 @@
         <v>191</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O40" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7692,7 +7692,7 @@
         <v>191</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O41" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7781,7 +7781,7 @@
         <v>191</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O42" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7870,7 +7870,7 @@
         <v>191</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O43" s="1" t="str">
         <f t="shared" si="2"/>
@@ -7959,7 +7959,7 @@
         <v>191</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O44" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8048,7 +8048,7 @@
         <v>191</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O45" s="1" t="str">
         <f t="shared" si="2"/>
@@ -8137,7 +8137,7 @@
         <v>191</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O46" s="1" t="str">
         <f t="shared" ref="O46:O51" si="4">SUBSTITUTE(F46,"hazr-","")&amp;"-osdisk"</f>
@@ -8226,7 +8226,7 @@
         <v>191</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O47" s="1" t="str">
         <f t="shared" si="4"/>
@@ -8315,7 +8315,7 @@
         <v>191</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O48" s="1" t="str">
         <f t="shared" si="4"/>
@@ -8404,7 +8404,7 @@
         <v>191</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O49" s="1" t="str">
         <f t="shared" si="4"/>
@@ -8493,7 +8493,7 @@
         <v>191</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O50" s="1" t="str">
         <f t="shared" si="4"/>
@@ -8652,7 +8652,7 @@
         <v>392</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I52" s="1">
         <v>2</v>
@@ -8667,10 +8667,10 @@
         <v>182</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O52" s="1" t="str">
         <f>SUBSTITUTE(F52,"hazr-","")&amp;"-osdisk"</f>
@@ -8737,7 +8737,7 @@
         <v>391</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>185</v>
@@ -8755,10 +8755,10 @@
         <v>182</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O53" s="1" t="str">
         <f>SUBSTITUTE(F53,"hazr-","")&amp;"-osdisk"</f>
@@ -14401,6 +14401,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -14544,15 +14553,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
   <ds:schemaRefs>
@@ -14570,6 +14570,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14585,12 +14593,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>